--- a/订单模拟.xlsx
+++ b/订单模拟.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派单\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3319F47F-F0E9-47D1-8168-26249B105722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A8758D-9596-46C4-9933-D0717570CA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{2C51E715-34DE-4CD0-BC5D-75FCCF988C66}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{2C51E715-34DE-4CD0-BC5D-75FCCF988C66}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -706,6 +706,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367D10D4-545D-44D1-877D-01666B47FA0A}">
   <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:31" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
